--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,114 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="D8" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -792,13 +799,19 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>500</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
@@ -845,13 +858,19 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>15600</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -898,8 +917,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,61 +944,69 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F12" s="3">
         <v>14700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>11400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>11900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>29900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>19000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>17200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>20100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>7800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>32800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>3100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3500</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1058,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,8 +1117,14 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1176,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1200,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>17800</v>
+      </c>
+      <c r="F17" s="3">
         <v>25400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>18100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>21000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>38000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>28400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>25700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>31400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>16400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>11600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>35700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-18100</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-28400</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-25700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-31400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-16400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-11600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-35700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,114 +1341,128 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>700</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-15400</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-35900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-27500</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-25400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-31200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-16700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-14000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-36700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-4400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1435,61 +1514,73 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-23000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-15900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-19200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-36100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-27700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-25600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-31400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-16800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-14200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-36800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1541,8 +1632,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1691,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-23000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-15900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-19200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-36100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-27700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-25600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-31400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-16800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-14200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-36800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-23000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-15900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-19200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-36100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-27700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-25600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-31400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-14200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-36800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1868,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1927,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1986,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +2045,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-23000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-15900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-19200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-36100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-27700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-25600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-31400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-14200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-36800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2222,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-23000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-15900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-19200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-36100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-27700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-25600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-31400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-14200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-36800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2372,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,47 +2395,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F41" s="3">
         <v>14700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>25900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>53100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>179300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>198500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>223400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>247100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>274700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>133500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>142500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2277,26 +2450,32 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>109600</v>
+      </c>
+      <c r="F42" s="3">
         <v>118300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>116800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>96300</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2309,11 +2488,11 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2330,13 +2509,19 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>8000</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2344,15 +2529,15 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,11 +2547,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2383,8 +2568,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2436,47 +2627,53 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F45" s="3">
         <v>6100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,47 +2686,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>172400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>124600</v>
+      </c>
+      <c r="F46" s="3">
         <v>139100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>149300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>156200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>186600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>202800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>226600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>251300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>278700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>134300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>142900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,8 +2745,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2595,47 +2804,53 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F48" s="3">
         <v>25300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>25900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>26600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>24800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>21100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,20 +2863,26 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F49" s="3">
         <v>22300</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2674,11 +2895,11 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2701,8 +2922,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2981,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,19 +3040,25 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2831,23 +3070,23 @@
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +3099,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,47 +3158,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>173700</v>
+      </c>
+      <c r="F54" s="3">
         <v>186700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>175200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>182800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>211400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>223900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>242600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>252700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>280000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>139500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>147000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,8 +3217,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3244,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,47 +3267,49 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>5500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>12000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,8 +3322,14 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3114,47 +3381,53 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>21900</v>
+      </c>
+      <c r="F59" s="3">
         <v>25000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>24500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>7100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>17100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>14900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>7100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,47 +3440,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F60" s="3">
         <v>28300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>11600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>31600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>19100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>19200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>16800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,8 +3499,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3273,47 +3558,53 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>22300</v>
+      </c>
+      <c r="F62" s="3">
         <v>20400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>20700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>19000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>18900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>16100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>15700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3617,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3676,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3735,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,47 +3794,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F66" s="3">
         <v>48700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>30000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>30600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>50600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>35100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>30600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>19200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>16900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>10600</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3538,8 +3853,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3880,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3935,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3994,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3695,17 +4030,17 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>194000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="O70" s="3">
         <v>194000</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3718,8 +4053,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,47 +4112,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-289500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-286200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-270600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-247600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-231700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-212400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-176300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-148700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-123100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-91700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-74900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-60700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3824,8 +4171,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4230,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4289,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,47 +4348,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>184200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>125700</v>
+      </c>
+      <c r="F76" s="3">
         <v>137900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>145300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>152200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>160800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>188700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>212000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>233500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>261300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-71400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-57600</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4036,8 +4407,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4466,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-15600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-23000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-15900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-19200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-36100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-27700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-25600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-31400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-14200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-36800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,22 +4616,24 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>700</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -4257,25 +4654,31 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4730,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4789,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4848,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4907,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4966,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-17600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-11000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-26800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-17400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-20600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-27700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-12200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-7300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-18700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +5052,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-4400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +5166,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +5225,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F94" s="3">
         <v>6600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-22300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-99400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-4300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5311,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4899,8 +5366,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5425,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5484,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,23 +5543,29 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>6100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -5082,37 +5573,43 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>154900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>151500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5164,57 +5661,69 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-11200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-27200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-126200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-19200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-24800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-23800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-27600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>142700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-9000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>132600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,107 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>16100</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
@@ -772,8 +776,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -805,17 +809,20 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,17 +871,20 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
         <v>15600</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +933,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +959,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E12" s="3">
         <v>13000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>32800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3500</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1081,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1123,8 +1143,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1205,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,76 +1228,80 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E17" s="3">
         <v>21800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>25400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>38000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>25700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>31400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1287,41 +1317,44 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>-25700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,17 +1376,18 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>2400</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1369,50 +1403,53 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1428,41 +1465,44 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-25400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-31200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-16700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-14000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-4400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1520,67 +1560,73 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-36100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-31400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1638,8 +1684,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1746,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-36100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-36100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5100</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1932,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1994,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2056,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,17 +2118,20 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2400</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2077,100 +2147,106 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-36100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2304,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-36100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2459,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,50 +2483,51 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25100</v>
+      </c>
+      <c r="E41" s="3">
         <v>28000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>53100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>179300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>198500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>223400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>247100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>274700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>142500</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,29 +2543,32 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E42" s="3">
         <v>129100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>109600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>118300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>116800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>96300</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2494,8 +2584,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2515,17 +2605,20 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>8000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,12 +2628,12 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2553,8 +2646,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2574,8 +2667,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2633,50 +2729,53 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E45" s="3">
         <v>7400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,50 +2791,53 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E46" s="3">
         <v>172400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>124600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>139100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>149300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>156200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>186600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>202800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>226600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>251300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>278700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>134300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>142900</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,8 +2853,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2810,50 +2915,53 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E48" s="3">
         <v>24100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>25300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1900</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2869,8 +2977,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2878,14 +2989,14 @@
         <v>23700</v>
       </c>
       <c r="E49" s="3">
+        <v>23700</v>
+      </c>
+      <c r="F49" s="3">
         <v>24300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2901,8 +3012,8 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2928,8 +3039,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3101,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3163,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3076,20 +3196,20 @@
         <v>0</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,8 +3225,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,50 +3287,53 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>208400</v>
+      </c>
+      <c r="E54" s="3">
         <v>220200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>173700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>186700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>175200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>182800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>211400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>223900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>242600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>252700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>280000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>139500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>147000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3349,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3375,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,50 +3399,51 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3328,8 +3459,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3387,50 +3521,53 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E59" s="3">
         <v>11800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,50 +3583,53 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E60" s="3">
         <v>14100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>25800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8400</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,13 +3645,16 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -3564,50 +3707,53 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E62" s="3">
         <v>21900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15700</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2200</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3769,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3831,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3893,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,50 +3955,53 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E66" s="3">
         <v>36100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>48000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>50600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>19200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4017,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4043,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4103,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4165,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4036,13 +4204,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>194000</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="Q70" s="3">
         <v>0</v>
@@ -4059,8 +4227,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,50 +4289,53 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-306800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-289500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-286200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-270600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-247600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-231700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-212400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-176300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-148700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-123100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-91700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-74900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-60700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4351,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4413,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4475,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,50 +4537,53 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>169800</v>
+      </c>
+      <c r="E76" s="3">
         <v>184200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>125700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>137900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>145300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>152200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>160800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>188700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>212000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>233500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>261300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-71400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-57600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4599,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4661,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-36100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,25 +4816,26 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700</v>
-      </c>
-      <c r="F83" s="3">
-        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -4660,16 +4859,16 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4677,8 +4876,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4938,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +5000,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5062,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5124,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5186,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-20700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-15300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-17600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-11000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-26800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5274,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5396,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5458,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-22300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-99400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
       <c r="M94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5546,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5606,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5668,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5730,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,26 +5792,29 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>57500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -5579,28 +5825,28 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>154900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>151500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
@@ -5608,8 +5854,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5667,63 +5916,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E102" s="3">
         <v>18300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-126200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-23800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-27600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>142700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>132600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,114 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>16100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
@@ -779,8 +783,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -812,20 +816,23 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
@@ -874,19 +881,22 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="3">
-        <v>15600</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>15700</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
@@ -936,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +973,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E12" s="3">
         <v>14000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>29900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>32800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3500</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,31 +1101,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1146,31 +1166,34 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1208,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="E17" s="3">
-        <v>21800</v>
+        <v>19300</v>
       </c>
       <c r="F17" s="3">
-        <v>17800</v>
+        <v>21000</v>
       </c>
       <c r="G17" s="3">
-        <v>25400</v>
+        <v>17200</v>
       </c>
       <c r="H17" s="3">
-        <v>18100</v>
+        <v>24800</v>
       </c>
       <c r="I17" s="3">
-        <v>21000</v>
+        <v>17600</v>
       </c>
       <c r="J17" s="3">
+        <v>20900</v>
+      </c>
+      <c r="K17" s="3">
         <v>38000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>31400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-23000</v>
       </c>
       <c r="E18" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-19300</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-20900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>-25700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-31400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-35700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,16 +1410,17 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>2400</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>3</v>
@@ -1406,126 +1440,132 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-22300</v>
       </c>
       <c r="E21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-18700</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-20700</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-25400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-31200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-36700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-4400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1563,93 +1603,99 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-23000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-36100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-31400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1687,8 +1733,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-36100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-31400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-36800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-23000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-36100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5100</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,16 +2188,19 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>-2400</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -2150,103 +2220,109 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-23000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-36100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5100</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-23000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-36100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5100</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,53 +2570,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E41" s="3">
         <v>25100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>53100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>179300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>198500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>223400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>247100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>274700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>142500</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,32 +2633,35 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E42" s="3">
         <v>130700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>129100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>109600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>118300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>116800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>96300</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,8 +2677,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2608,22 +2698,25 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>8000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2631,12 +2724,12 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,8 +2742,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2670,31 +2763,34 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2732,53 +2828,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>6100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>6700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,53 +2893,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>148900</v>
+      </c>
+      <c r="E46" s="3">
         <v>161000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>172400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>124600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>139100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>149300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>156200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>186600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>202800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>226600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>251300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>278700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>134300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>142900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,31 +2958,34 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2918,53 +3023,56 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E48" s="3">
         <v>23700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>25300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,31 +3088,34 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>23700</v>
+        <v>23600</v>
       </c>
       <c r="E49" s="3">
         <v>23700</v>
       </c>
       <c r="F49" s="3">
+        <v>23700</v>
+      </c>
+      <c r="G49" s="3">
         <v>24300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -3015,8 +3126,8 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3042,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,31 +3283,34 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3199,20 +3319,20 @@
         <v>0</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3348,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,53 +3413,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>195300</v>
+      </c>
+      <c r="E54" s="3">
         <v>208400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>220200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>173700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>186700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>175200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>182800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>211400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>223900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>242600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>252700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>280000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>139500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>147000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,53 +3530,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E57" s="3">
         <v>5500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,31 +3593,34 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3524,53 +3658,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>11400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>11800</v>
-      </c>
-      <c r="F59" s="3">
-        <v>21900</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="H59" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>24500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,53 +3723,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E60" s="3">
         <v>16900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>25800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,31 +3788,34 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>19100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>19500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>20100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3710,53 +3853,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>21600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>21900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>22300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>20400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>20700</v>
-      </c>
-      <c r="I62" s="3">
-        <v>19000</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>18900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15700</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3918,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,53 +4113,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E66" s="3">
         <v>38600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>50600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4207,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>194000</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4230,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,53 +4463,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-328000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-306800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-289500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-286200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-270600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-247600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-231700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-212400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-176300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-148700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-123100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-91700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-74900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-60700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,53 +4723,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E76" s="3">
         <v>169800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>184200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>125700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>137900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>145300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>152200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>160800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>188700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>212000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>233500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>261300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-71400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-57600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-23000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-36100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5100</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,25 +5015,26 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -4862,16 +5061,16 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -4879,8 +5078,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-20700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-15300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-17600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-11000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-18700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5495,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5284,61 +5505,64 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5688,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5470,61 +5700,64 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-18500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-99400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
       <c r="N94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,31 +5780,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5609,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,31 +6038,34 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>57500</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -5828,28 +6074,28 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>154900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>151500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -5857,31 +6103,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5919,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-27200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-126200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-24800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-23800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-27600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>142700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>132600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,106 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -765,12 +768,12 @@
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>16100</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -786,8 +789,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -819,23 +822,26 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,23 +890,26 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
         <v>15700</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -949,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,73 +986,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E12" s="3">
         <v>17700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>29900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>32800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3500</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,13 +1120,16 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>21000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1130,8 +1149,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1169,35 +1188,38 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>500</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
       </c>
       <c r="J15" s="3">
+        <v>500</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1234,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E17" s="3">
         <v>23000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>38000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>31400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>35700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-23000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-19300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-17200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-24800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-17600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-25700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-31400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-35700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1443,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1443,106 +1476,112 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-22300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-18700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-24200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20700</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-25400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-36700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-4400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1567,8 +1606,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1606,78 +1645,84 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-23000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-31400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-2200</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1697,8 +1742,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1736,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-23000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-36100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-31400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-36800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-23000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-36100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2257,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2223,106 +2292,112 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-23000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-36100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-36800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-23000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-36100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-36800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,56 +2656,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E41" s="3">
         <v>12100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>25100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>179300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>198500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>223400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>247100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>274700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>142500</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2636,35 +2722,38 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E42" s="3">
         <v>132800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>130700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>129100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>109600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>118300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>116800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>96300</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2680,8 +2769,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2701,8 +2790,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2712,12 +2804,12 @@
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>8000</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2727,12 +2819,12 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2745,8 +2837,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2766,8 +2858,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2792,8 +2887,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2831,13 +2926,16 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>3300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2845,42 +2943,42 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>6700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2896,56 +2994,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>132400</v>
+      </c>
+      <c r="E46" s="3">
         <v>148900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>161000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>172400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>124600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>139100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>149300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>156200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>186600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>202800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>226600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>251300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>278700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>134300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>142900</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2961,8 +3062,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2987,8 +3091,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3026,56 +3130,59 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E48" s="3">
         <v>22800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>25300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>26600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,34 +3198,37 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E49" s="3">
         <v>23600</v>
-      </c>
-      <c r="E49" s="3">
-        <v>23700</v>
       </c>
       <c r="F49" s="3">
         <v>23700</v>
       </c>
       <c r="G49" s="3">
+        <v>23700</v>
+      </c>
+      <c r="H49" s="3">
         <v>24300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>22300</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -3129,8 +3239,8 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3156,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3402,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3312,8 +3431,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3322,20 +3441,20 @@
         <v>0</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,56 +3538,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>157200</v>
+      </c>
+      <c r="E54" s="3">
         <v>195300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>220200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>173700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>186700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>175200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>182800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>211400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>223900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>242600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>252700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>280000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>139500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>147000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,8 +3660,9 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3540,47 +3670,47 @@
         <v>4900</v>
       </c>
       <c r="E57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,35 +3726,38 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1200</v>
       </c>
       <c r="H58" s="3">
         <v>1200</v>
       </c>
       <c r="I58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3661,13 +3794,16 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>600</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -3675,42 +3811,42 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>8000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>24500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,56 +3862,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E60" s="3">
         <v>20300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>14100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>25800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3791,35 +3930,38 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E61" s="3">
         <v>19100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3856,8 +3998,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3882,30 +4027,30 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>18900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15700</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3921,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,56 +4270,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E66" s="3">
         <v>41600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>36100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>50600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4181,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4378,13 +4545,13 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3">
         <v>194000</v>
       </c>
       <c r="R70" s="3">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="S70" s="3">
         <v>0</v>
@@ -4401,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,56 +4636,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-363600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-328000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-306800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-289500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-286200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-270600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-247600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-231700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-212400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-176300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-148700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-123100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-91700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-74900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-60700</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,56 +4908,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E76" s="3">
         <v>153700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>169800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>184200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>125700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>137900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>145300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>152200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>160800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>188700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>212000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>233500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>261300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-71400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-57600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-23000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-36100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-36800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5213,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5028,7 +5226,7 @@
         <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -5064,16 +5262,16 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5081,8 +5279,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-15300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-17600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-17400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-23700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-27700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5715,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5508,61 +5728,64 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5917,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>26700</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-18500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>6600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-99400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-100</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-1300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5807,8 +6040,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5846,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,34 +6283,37 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>57500</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -6077,28 +6322,28 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>154900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>151500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6106,8 +6351,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6132,8 +6380,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6171,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-126200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-24800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-23800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-27600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>142700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>132600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
+      <c r="E8" s="3">
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>16100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -792,8 +796,8 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -825,26 +829,29 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>500</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -893,26 +900,29 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>15700</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E12" s="3">
         <v>14000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>13000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>29900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>32800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3500</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,17 +1140,20 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>21000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,8 +1172,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1191,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1200,29 +1223,29 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>700</v>
-      </c>
-      <c r="I15" s="3">
-        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
       </c>
       <c r="K15" s="3">
+        <v>500</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1308,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E17" s="3">
         <v>18400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>19300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>20900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>38000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>35700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-23000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-17200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-17600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-20900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>-25700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-31400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-11600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-35700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1477,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1479,109 +1513,115 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-17800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-24200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20700</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-25400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-14000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-36700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-4400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1609,8 +1649,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1648,85 +1688,91 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-37700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-21200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-23000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-36100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-31400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2200</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1745,8 +1791,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1784,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-21200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-23000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-19200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-36100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-31400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-36800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-23000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-36100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2327,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2295,109 +2365,115 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-23000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-36100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-23000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-36100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,59 +2743,60 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E41" s="3">
         <v>19500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>25100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>179300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>198500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>223400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>247100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>274700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>133500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>142500</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,38 +2812,41 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E42" s="3">
         <v>107500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>132800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>130700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>129100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>109600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>118300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>116800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>96300</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2862,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2793,8 +2883,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2807,12 +2900,12 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>8000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2822,12 +2915,12 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2840,8 +2933,8 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2861,8 +2954,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2890,8 +2986,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2929,59 +3025,62 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>3300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>2800</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>6700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,59 +3096,62 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E46" s="3">
         <v>132400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>148900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>161000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>172400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>124600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>149300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>156200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>186600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>202800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>226600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>251300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>278700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>134300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>142900</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,8 +3167,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3094,8 +3199,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3133,59 +3238,62 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E48" s="3">
         <v>22100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,37 +3309,40 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23600</v>
-      </c>
-      <c r="F49" s="3">
-        <v>23700</v>
       </c>
       <c r="G49" s="3">
         <v>23700</v>
       </c>
       <c r="H49" s="3">
+        <v>23700</v>
+      </c>
+      <c r="I49" s="3">
         <v>24300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>22300</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -3242,8 +3353,8 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3434,8 +3554,8 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3444,20 +3564,20 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,59 +3664,62 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>135900</v>
+      </c>
+      <c r="E54" s="3">
         <v>157200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>195300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>220200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>173700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>186700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>175200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>211400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>223900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>242600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>252700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>280000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>139500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>147000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,59 +3791,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4900</v>
+        <v>2800</v>
       </c>
       <c r="E57" s="3">
         <v>4900</v>
       </c>
       <c r="F57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G57" s="3">
         <v>5500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,8 +3860,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3738,29 +3872,29 @@
         <v>1500</v>
       </c>
       <c r="E58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F58" s="3">
         <v>1400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1200</v>
       </c>
       <c r="I58" s="3">
         <v>1200</v>
       </c>
       <c r="J58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3797,59 +3931,62 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>8000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>24500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>14900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,59 +4002,62 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E60" s="3">
         <v>17700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>25800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8400</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,38 +4073,41 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E61" s="3">
         <v>18800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4001,8 +4144,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4030,30 +4176,30 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>18900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15700</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,59 +4428,62 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E66" s="3">
         <v>36400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>50600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>35100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>18700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4548,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3">
         <v>194000</v>
       </c>
       <c r="S70" s="3">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="T70" s="3">
         <v>0</v>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,59 +4810,62 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-384700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-363600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-328000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-306800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-289500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-286200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-270600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-247600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-231700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-212400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-176300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-148700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-123100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-91700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-74900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-60700</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,59 +5094,62 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E76" s="3">
         <v>120800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>153700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>169800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>184200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>125700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>137900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>145300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>152200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>160800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>188700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>212000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>233500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>261300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-71400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-57600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-23000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-36100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,13 +5412,14 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
@@ -5229,7 +5428,7 @@
         <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -5265,16 +5464,16 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5282,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-15300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-17600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-17400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-27700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4300</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,13 +5936,14 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -5731,61 +5952,64 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E94" s="3">
         <v>26700</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-18500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>6600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-99400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
       <c r="P94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-1300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6043,8 +6277,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,37 +6529,40 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>57500</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -6325,28 +6571,28 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>154900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>151500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6354,8 +6600,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6383,8 +6632,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6422,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E102" s="3">
         <v>7400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-126200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-24800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-23800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-27600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>142700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>132600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,134 +656,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>16100</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -799,8 +803,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -832,29 +836,32 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,29 +910,32 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>15700</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E12" s="3">
         <v>17000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>14000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>13000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>29900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>20100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>32800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3500</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,20 +1160,23 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>21000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1175,8 +1195,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1214,41 +1234,44 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
       </c>
       <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
       </c>
       <c r="L15" s="3">
+        <v>500</v>
+      </c>
+      <c r="M15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E17" s="3">
         <v>22400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>18400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>21000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>38000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-17200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-17600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-20900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>-25700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-11600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-35700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1516,112 +1550,118 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-21800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-17800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-24200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20700</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-25400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-14000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-36700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1652,8 +1692,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1691,91 +1731,97 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-21200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-23000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-36100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-36800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>-2200</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1794,8 +1840,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1833,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-21200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-23000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-19200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-36100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-27700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-36800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-23000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-36100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2368,112 +2438,118 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-23000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-36100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-27700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-23000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-36100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-27700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,62 +2830,63 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E41" s="3">
         <v>12800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>25100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>28000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>25900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>179300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>198500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>223400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>247100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>274700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>133500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>142500</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,41 +2902,44 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E42" s="3">
         <v>92700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>107500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>132800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>130700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>129100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>109600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>118300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>116800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>96300</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2865,8 +2955,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2886,13 +2976,16 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>3000</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2903,12 +2996,12 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>8000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2918,12 +3011,12 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2936,8 +3029,8 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2957,8 +3050,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2989,8 +3085,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3028,62 +3124,65 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>3300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>6700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,62 +3198,65 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E46" s="3">
         <v>111900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>132400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>148900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>161000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>172400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>124600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>139100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>149300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>156200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>186600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>202800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>226600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>251300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>278700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>134300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>142900</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3272,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3202,8 +3307,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3241,62 +3346,65 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E48" s="3">
         <v>21500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,8 +3420,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3321,31 +3432,31 @@
         <v>2500</v>
       </c>
       <c r="E49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F49" s="3">
         <v>2600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>23700</v>
       </c>
       <c r="H49" s="3">
         <v>23700</v>
       </c>
       <c r="I49" s="3">
+        <v>23700</v>
+      </c>
+      <c r="J49" s="3">
         <v>24300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>22300</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -3356,8 +3467,8 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3557,8 +3677,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3567,20 +3687,20 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,62 +3790,65 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E54" s="3">
         <v>135900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>157200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>195300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>208400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>220200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>173700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>186700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>175200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>182800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>211400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>223900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>242600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>252700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>280000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>139500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>147000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,62 +3922,63 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2800</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4900</v>
       </c>
       <c r="F57" s="3">
         <v>4900</v>
       </c>
       <c r="G57" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H57" s="3">
         <v>5500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,41 +3994,44 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E58" s="3">
         <v>1500</v>
       </c>
       <c r="F58" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>1200</v>
       </c>
       <c r="J58" s="3">
         <v>1200</v>
       </c>
       <c r="K58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3934,62 +4068,65 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>8000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>24500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>14900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,62 +4142,65 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E60" s="3">
         <v>14400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>20300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>19200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,41 +4216,44 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E61" s="3">
         <v>18300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4147,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4179,30 +4325,30 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>18900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15700</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,62 +4586,65 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E66" s="3">
         <v>32800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>38600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>35100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4719,13 +4887,13 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
-        <v>194000</v>
+        <v>0</v>
       </c>
       <c r="S70" s="3">
         <v>194000</v>
       </c>
       <c r="T70" s="3">
-        <v>0</v>
+        <v>194000</v>
       </c>
       <c r="U70" s="3">
         <v>0</v>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,62 +4984,65 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-403100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-384700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-363600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-328000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-306800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-289500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-286200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-270600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-247600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-231700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-212400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-176300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-148700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-123100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-91700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-74900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-60700</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,62 +5280,65 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E76" s="3">
         <v>103100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>120800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>153700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>169800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>184200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>125700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>137900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>145300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>152200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>160800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>188700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>212000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>233500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>261300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-71400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-57600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-23000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-36100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-27700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,16 +5611,17 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>500</v>
@@ -5431,7 +5630,7 @@
         <v>500</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -5467,16 +5666,16 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
@@ -5484,8 +5683,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-15300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-23700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-18700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4300</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,16 +6157,17 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -5955,61 +6176,64 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E94" s="3">
         <v>15800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26700</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-18500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>6600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-99400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-100</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6280,8 +6514,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,40 +6775,43 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>57500</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -6574,28 +6820,28 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>154900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>151500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
@@ -6603,8 +6849,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6635,8 +6884,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6674,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-11200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-27200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-126200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-24800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-23800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>142700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>132600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5600</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PYXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="92">
   <si>
     <t>PYXS</t>
   </si>
@@ -656,121 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,29 +785,29 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3">
         <v>2800</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>16100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -813,11 +820,11 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -846,38 +853,44 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
+      <c r="E9" s="3">
+        <v>2400</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="3">
-        <v>0</v>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +936,14 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -932,29 +951,29 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3">
         <v>2800</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>15700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,8 +1019,14 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,85 +1054,93 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F12" s="3">
         <v>17800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>17100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>17000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>14000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>17700</v>
       </c>
       <c r="I12" s="3">
         <v>14000</v>
       </c>
       <c r="J12" s="3">
+        <v>17700</v>
+      </c>
+      <c r="K12" s="3">
+        <v>14000</v>
+      </c>
+      <c r="L12" s="3">
         <v>13000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>11600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>14700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>11400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>11900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>29900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>19000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>17200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>20100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>7200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>32800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>3100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>3500</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1216,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1197,15 +1236,15 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>21000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,11 +1260,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1260,50 +1299,56 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F15" s="3">
         <v>500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>600</v>
-      </c>
-      <c r="H15" s="3">
-        <v>700</v>
       </c>
       <c r="I15" s="3">
         <v>600</v>
       </c>
       <c r="J15" s="3">
+        <v>700</v>
+      </c>
+      <c r="K15" s="3">
+        <v>600</v>
+      </c>
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1382,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1414,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F17" s="3">
         <v>22800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>21900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>22400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>18400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>23000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>19300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>21000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>17200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>24800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>17600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>20900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>38000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>28400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>25700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>31400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>16400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>11600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>35700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-22800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-19100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-22400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-23000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-17200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-17600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-20900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-25700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-31400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-16400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-11600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-35700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-4600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1611,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1590,118 +1657,130 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-2200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-22300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-18500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-21800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-17800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-22300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-18700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-16500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-24200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-17000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-20700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-25400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-31200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-16700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-14000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-7900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-36700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-4400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1738,11 +1817,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1777,85 +1856,97 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-18100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-37700</v>
       </c>
       <c r="H23" s="3">
         <v>-21200</v>
       </c>
       <c r="I23" s="3">
+        <v>-37700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-17300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-15600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-23000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-15900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-36100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-25600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-31400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-16800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-14200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-8100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-36800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-4600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1863,20 +1954,20 @@
         <v>3</v>
       </c>
       <c r="E24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-2200</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1892,11 +1983,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1931,8 +2022,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2105,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-22000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-18400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-35600</v>
       </c>
       <c r="H26" s="3">
         <v>-21200</v>
       </c>
       <c r="I26" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-17300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-15600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-23000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-15900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-19200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-36100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-25600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-31400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-16800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-14200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-8100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-36800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-4600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-22000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-18400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-35600</v>
       </c>
       <c r="H27" s="3">
         <v>-21200</v>
       </c>
       <c r="I27" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-17300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-15600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-23000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-15900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-19200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-36100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-25600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-31400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-16800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-14200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-8100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-36800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-4600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2354,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2437,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2520,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2603,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2514,118 +2653,130 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>2200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-22000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-18400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-35600</v>
       </c>
       <c r="H33" s="3">
         <v>-21200</v>
       </c>
       <c r="I33" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-17300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-15600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-23000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-15900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-19200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-36100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-25600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-31400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-16800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-14200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-8100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-36800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-4600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2852,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-22000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-18400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-35600</v>
       </c>
       <c r="H35" s="3">
         <v>-21200</v>
       </c>
       <c r="I35" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-17300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-15600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-23000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-15900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-19200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-36100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-25600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-31400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-16800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-14200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-8100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-36800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-4600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +3058,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,71 +3089,73 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F41" s="3">
         <v>8900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>25100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>28000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>14700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>25900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>53100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>179300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>198500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>223400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>247100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>274700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>133500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>142500</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,50 +3168,56 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F42" s="3">
         <v>67300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>78200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>92700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>107500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>132800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>130700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>129100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>109600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>118300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>116800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>96300</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,11 +3230,11 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3072,8 +3251,14 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3081,44 +3266,44 @@
         <v>3</v>
       </c>
       <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>8000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3">
         <v>600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,11 +3313,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3149,8 +3334,14 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3187,11 +3378,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3226,71 +3417,77 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3">
+        <v>2500</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>6700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>4300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>4200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>3900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,71 +3500,77 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>72100</v>
+      </c>
+      <c r="F46" s="3">
         <v>83100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>100000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>111900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>132400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>148900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>161000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>172400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>124600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>139100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>149300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>156200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>186600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>202800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>226600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>251300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>278700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>134300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>142900</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,8 +3583,14 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3418,11 +3627,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3457,71 +3666,77 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F48" s="3">
         <v>20100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>20800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>22100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>22800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>23700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>24100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>24800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>25300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>25900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>26600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>24800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>21100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>16000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,49 +3749,55 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>2400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>23600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>23700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>23700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>24300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>22300</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -3584,11 +3805,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3611,8 +3832,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3915,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3998,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3803,33 +4042,33 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>3600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3842,8 +4081,14 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,71 +4164,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>91500</v>
+      </c>
+      <c r="F54" s="3">
         <v>105600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>123200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>135900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>157200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>195300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>208400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>220200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>173700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>186700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>175200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>182800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>211400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>223900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>242600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>252700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>280000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>139500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>147000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4247,14 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4282,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,71 +4313,73 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F57" s="3">
         <v>9800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>9400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>4900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>7100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>7800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>12000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4131,49 +4392,55 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>1200</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4208,71 +4475,77 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+      <c r="E59" s="3">
+        <v>400</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>8000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>7200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>24500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>7100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>17100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>6800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>14900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,71 +4558,77 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F60" s="3">
         <v>19400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>17700</v>
-      </c>
-      <c r="F60" s="3">
-        <v>14400</v>
       </c>
       <c r="G60" s="3">
         <v>17700</v>
       </c>
       <c r="H60" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I60" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J60" s="3">
         <v>20300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>16900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>25800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>28300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>31600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>19100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>19200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>16800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>8400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,50 +4641,56 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F61" s="3">
         <v>17400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>17900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>18300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>18800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>19100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>19500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>19800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>20100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>20400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>20700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>19000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4439,8 +4724,14 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4477,33 +4768,33 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>18900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>16100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>15700</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2200</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4516,8 +4807,14 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4890,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4973,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,71 +5056,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>38100</v>
+      </c>
+      <c r="F66" s="3">
         <v>36800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>35600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>32800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>36400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>41600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>38600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>36100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>48000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>48700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>30000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>30600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>50600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>35100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>30600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>19200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>18700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>16900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>10600</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +5139,14 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5174,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5253,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5336,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5061,17 +5396,17 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>194000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="W70" s="3">
         <v>194000</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5419,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,71 +5502,77 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-466400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-443200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-425100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-403100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-384700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-363600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-328000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-306800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-289500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-286200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-270600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-247600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-231700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-212400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-176300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-148700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-123100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-91700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-74900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-60700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5585,14 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5668,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5751,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,71 +5834,77 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>53400</v>
+      </c>
+      <c r="F76" s="3">
         <v>68800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>87600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>103100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>120800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>153700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>169800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>184200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>125700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>137900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>145300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>152200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>160800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>188700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>212000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>233500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>261300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-71400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-57600</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5917,14 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +6000,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-22000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-18400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-21200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-35600</v>
       </c>
       <c r="H81" s="3">
         <v>-21200</v>
       </c>
       <c r="I81" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-17300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-15600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-23000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-15900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-19200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-36100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-27700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-25600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-31400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-16800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-14200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-8100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-36800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-4600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,34 +6206,36 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -5871,25 +6268,31 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
       <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6368,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6451,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6534,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6617,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6700,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-17300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-22500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-19300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-20700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-15300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-17600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-11000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-26800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-17400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-23700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-27700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-12200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-7300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-18700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-3200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6818,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6980,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +7063,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F94" s="3">
         <v>11500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>15300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>15800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>26700</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-18500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>10200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>6600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-22300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-99400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +7181,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6754,11 +7221,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6793,8 +7260,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7343,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7426,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,85 +7509,97 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>100</v>
-      </c>
       <c r="H100" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>100</v>
       </c>
       <c r="J100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K100" s="3">
+        <v>100</v>
+      </c>
+      <c r="L100" s="3">
         <v>57500</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>154900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>151500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7139,11 +7636,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7178,81 +7675,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-6700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>18300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-11200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-27200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-126200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-19200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-23800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-27600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>142700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-9000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>132600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
